--- a/plants_data/SFI_ALD_Petrochemicals_Sample_EU_NA_Apr_2022.xlsx
+++ b/plants_data/SFI_ALD_Petrochemicals_Sample_EU_NA_Apr_2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F048846-8DF5-4323-94D5-79C3F0515F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9976C187-9B33-4E00-BBB3-543BD2517113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11760" yWindow="12864" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{49FED9BB-E9B4-4298-B606-A2033C4439F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{49FED9BB-E9B4-4298-B606-A2033C4439F2}"/>
   </bookViews>
   <sheets>
     <sheet name="About - General" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5817" uniqueCount="1430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5858" uniqueCount="1436">
   <si>
     <t>Spatial Finance Initiative Petrochemicals Database for Europe and North America (April 2022)</t>
   </si>
@@ -4456,6 +4456,24 @@
   </si>
   <si>
     <t>Cluster</t>
+  </si>
+  <si>
+    <t>BEL1</t>
+  </si>
+  <si>
+    <t>BEL2</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>NL1</t>
+  </si>
+  <si>
+    <t>NL2</t>
+  </si>
+  <si>
+    <t>NL3</t>
   </si>
 </sst>
 </file>
@@ -6766,9 +6784,9 @@
       </c>
       <c r="AG7" s="9"/>
     </row>
-    <row r="8" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
-        <v>1</v>
+    <row r="8" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>1430</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>130</v>
@@ -6857,9 +6875,9 @@
       </c>
       <c r="AG8" s="9"/>
     </row>
-    <row r="9" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
-        <v>1</v>
+    <row r="9" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>1430</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>143</v>
@@ -6948,9 +6966,9 @@
       </c>
       <c r="AG9" s="9"/>
     </row>
-    <row r="10" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
-        <v>1</v>
+    <row r="10" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>1430</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>144</v>
@@ -7039,9 +7057,9 @@
       </c>
       <c r="AG10" s="9"/>
     </row>
-    <row r="11" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6">
-        <v>1</v>
+    <row r="11" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>1430</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>145</v>
@@ -7130,9 +7148,9 @@
       </c>
       <c r="AG11" s="9"/>
     </row>
-    <row r="12" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6">
-        <v>1</v>
+    <row r="12" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>1430</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>146</v>
@@ -7234,9 +7252,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6">
-        <v>1</v>
+    <row r="13" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>1430</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>151</v>
@@ -7322,9 +7340,9 @@
       </c>
       <c r="AG13" s="9"/>
     </row>
-    <row r="14" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6">
-        <v>2</v>
+    <row r="14" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>1431</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>159</v>
@@ -9679,9 +9697,9 @@
       </c>
       <c r="AG40" s="9"/>
     </row>
-    <row r="41" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6">
-        <v>3</v>
+    <row r="41" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>408</v>
@@ -9767,9 +9785,9 @@
       </c>
       <c r="AG41" s="9"/>
     </row>
-    <row r="42" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="6">
-        <v>3</v>
+    <row r="42" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>419</v>
@@ -9855,9 +9873,9 @@
       </c>
       <c r="AG42" s="9"/>
     </row>
-    <row r="43" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="6">
-        <v>3</v>
+    <row r="43" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>421</v>
@@ -9943,9 +9961,9 @@
       </c>
       <c r="AG43" s="9"/>
     </row>
-    <row r="44" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="6">
-        <v>3</v>
+    <row r="44" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>422</v>
@@ -10111,9 +10129,9 @@
       </c>
       <c r="AG45" s="9"/>
     </row>
-    <row r="46" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6">
-        <v>3</v>
+    <row r="46" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>429</v>
@@ -10185,9 +10203,9 @@
       </c>
       <c r="AG46" s="9"/>
     </row>
-    <row r="47" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="6">
-        <v>3</v>
+    <row r="47" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>434</v>
@@ -10259,9 +10277,9 @@
       </c>
       <c r="AG47" s="9"/>
     </row>
-    <row r="48" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="6">
-        <v>3</v>
+    <row r="48" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>435</v>
@@ -10333,9 +10351,9 @@
       </c>
       <c r="AG48" s="9"/>
     </row>
-    <row r="49" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6">
-        <v>3</v>
+    <row r="49" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>436</v>
@@ -10407,9 +10425,9 @@
       </c>
       <c r="AG49" s="9"/>
     </row>
-    <row r="50" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="6">
-        <v>3</v>
+    <row r="50" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>437</v>
@@ -10726,9 +10744,9 @@
       </c>
       <c r="AG53" s="9"/>
     </row>
-    <row r="54" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="6">
-        <v>3</v>
+    <row r="54" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>454</v>
@@ -10812,9 +10830,9 @@
       </c>
       <c r="AG54" s="9"/>
     </row>
-    <row r="55" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="6">
-        <v>3</v>
+    <row r="55" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>457</v>
@@ -10898,9 +10916,9 @@
       </c>
       <c r="AG55" s="9"/>
     </row>
-    <row r="56" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="6">
-        <v>3</v>
+    <row r="56" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>458</v>
@@ -11713,9 +11731,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="65" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="6">
-        <v>3</v>
+    <row r="65" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>485</v>
@@ -11801,9 +11819,9 @@
       </c>
       <c r="AG65" s="9"/>
     </row>
-    <row r="66" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="6">
-        <v>3</v>
+    <row r="66" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>489</v>
@@ -11884,9 +11902,9 @@
       </c>
       <c r="AG66" s="9"/>
     </row>
-    <row r="67" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="6">
-        <v>3</v>
+    <row r="67" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>490</v>
@@ -11967,9 +11985,9 @@
       </c>
       <c r="AG67" s="9"/>
     </row>
-    <row r="68" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="6">
-        <v>3</v>
+    <row r="68" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>491</v>
@@ -12050,9 +12068,9 @@
       </c>
       <c r="AG68" s="9"/>
     </row>
-    <row r="69" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="6">
-        <v>3</v>
+    <row r="69" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>492</v>
@@ -12133,9 +12151,9 @@
       </c>
       <c r="AG69" s="9"/>
     </row>
-    <row r="70" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="6">
-        <v>3</v>
+    <row r="70" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>493</v>
@@ -12216,9 +12234,9 @@
       </c>
       <c r="AG70" s="9"/>
     </row>
-    <row r="71" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="6">
-        <v>3</v>
+    <row r="71" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="6" t="s">
+        <v>1432</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>496</v>
@@ -13109,8 +13127,8 @@
       <c r="AG81" s="9"/>
     </row>
     <row r="82" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="6">
-        <v>4</v>
+      <c r="A82" s="6" t="s">
+        <v>1433</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>555</v>
@@ -13195,8 +13213,8 @@
       <c r="AG82" s="9"/>
     </row>
     <row r="83" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="6">
-        <v>4</v>
+      <c r="A83" s="6" t="s">
+        <v>1433</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>563</v>
@@ -13281,8 +13299,8 @@
       <c r="AG83" s="9"/>
     </row>
     <row r="84" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="6">
-        <v>4</v>
+      <c r="A84" s="6" t="s">
+        <v>1433</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>564</v>
@@ -13367,8 +13385,8 @@
       <c r="AG84" s="9"/>
     </row>
     <row r="85" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="6">
-        <v>4</v>
+      <c r="A85" s="6" t="s">
+        <v>1433</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>565</v>
@@ -13453,8 +13471,8 @@
       <c r="AG85" s="9"/>
     </row>
     <row r="86" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="6">
-        <v>6</v>
+      <c r="A86" s="6" t="s">
+        <v>1435</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>566</v>
@@ -13532,8 +13550,8 @@
       <c r="AG86" s="9"/>
     </row>
     <row r="87" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="6">
-        <v>4</v>
+      <c r="A87" s="6" t="s">
+        <v>1433</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>574</v>
@@ -13620,8 +13638,8 @@
       <c r="AG87" s="9"/>
     </row>
     <row r="88" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="6">
-        <v>4</v>
+      <c r="A88" s="6" t="s">
+        <v>1433</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>579</v>
@@ -13708,8 +13726,8 @@
       <c r="AG88" s="9"/>
     </row>
     <row r="89" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="6">
-        <v>4</v>
+      <c r="A89" s="6" t="s">
+        <v>1433</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>580</v>
@@ -13796,8 +13814,8 @@
       <c r="AG89" s="9"/>
     </row>
     <row r="90" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="6">
-        <v>4</v>
+      <c r="A90" s="6" t="s">
+        <v>1433</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>581</v>
@@ -13884,8 +13902,8 @@
       <c r="AG90" s="9"/>
     </row>
     <row r="91" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="6">
-        <v>4</v>
+      <c r="A91" s="6" t="s">
+        <v>1433</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>582</v>
@@ -13975,8 +13993,8 @@
       <c r="AG91" s="9"/>
     </row>
     <row r="92" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="6">
-        <v>5</v>
+      <c r="A92" s="6" t="s">
+        <v>1434</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>587</v>
@@ -14063,8 +14081,8 @@
       <c r="AG92" s="9"/>
     </row>
     <row r="93" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="6">
-        <v>5</v>
+      <c r="A93" s="6" t="s">
+        <v>1434</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>598</v>
@@ -14151,8 +14169,8 @@
       <c r="AG93" s="9"/>
     </row>
     <row r="94" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="6">
-        <v>5</v>
+      <c r="A94" s="6" t="s">
+        <v>1434</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>599</v>
@@ -14234,8 +14252,8 @@
       <c r="AG94" s="9"/>
     </row>
     <row r="95" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="6">
-        <v>5</v>
+      <c r="A95" s="6" t="s">
+        <v>1434</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>600</v>
@@ -14317,8 +14335,8 @@
       <c r="AG95" s="9"/>
     </row>
     <row r="96" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="6">
-        <v>4</v>
+      <c r="A96" s="6" t="s">
+        <v>1433</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>601</v>
@@ -31056,11 +31074,6 @@
         <filter val="Zeeland"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Netherlands"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="7">
       <filters>
         <filter val="Europe"/>
@@ -31072,6 +31085,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c95907cf-e9f9-4b92-a10f-5d23f887974d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E03E5363D60F6E41BBDBD2986891499D" ma:contentTypeVersion="11" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="723753e909a658b81c41a8b79ae01792">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c95907cf-e9f9-4b92-a10f-5d23f887974d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e3777ca4d9a00e3a0fcbf4dc5e7e1334" ns2:_="">
     <xsd:import namespace="c95907cf-e9f9-4b92-a10f-5d23f887974d"/>
@@ -31255,16 +31278,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c95907cf-e9f9-4b92-a10f-5d23f887974d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -31275,24 +31288,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82F1485-9B46-4DE7-8EF4-68C318268E4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c95907cf-e9f9-4b92-a10f-5d23f887974d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55D8B328-D93F-4E0D-94E2-653BFEE7AE74}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -31311,6 +31306,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82F1485-9B46-4DE7-8EF4-68C318268E4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c95907cf-e9f9-4b92-a10f-5d23f887974d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DF01CBF-A5C4-4282-859D-8EAB800F0387}">
   <ds:schemaRefs>

--- a/plants_data/SFI_ALD_Petrochemicals_Sample_EU_NA_Apr_2022.xlsx
+++ b/plants_data/SFI_ALD_Petrochemicals_Sample_EU_NA_Apr_2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9976C187-9B33-4E00-BBB3-543BD2517113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AE3B68-1B9D-482F-A9CB-873F60256474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{49FED9BB-E9B4-4298-B606-A2033C4439F2}"/>
   </bookViews>
@@ -31085,16 +31085,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c95907cf-e9f9-4b92-a10f-5d23f887974d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E03E5363D60F6E41BBDBD2986891499D" ma:contentTypeVersion="11" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="723753e909a658b81c41a8b79ae01792">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c95907cf-e9f9-4b92-a10f-5d23f887974d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e3777ca4d9a00e3a0fcbf4dc5e7e1334" ns2:_="">
     <xsd:import namespace="c95907cf-e9f9-4b92-a10f-5d23f887974d"/>
@@ -31278,6 +31268,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c95907cf-e9f9-4b92-a10f-5d23f887974d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -31288,6 +31288,24 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82F1485-9B46-4DE7-8EF4-68C318268E4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c95907cf-e9f9-4b92-a10f-5d23f887974d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55D8B328-D93F-4E0D-94E2-653BFEE7AE74}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -31306,24 +31324,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82F1485-9B46-4DE7-8EF4-68C318268E4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c95907cf-e9f9-4b92-a10f-5d23f887974d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DF01CBF-A5C4-4282-859D-8EAB800F0387}">
   <ds:schemaRefs>

--- a/plants_data/SFI_ALD_Petrochemicals_Sample_EU_NA_Apr_2022.xlsx
+++ b/plants_data/SFI_ALD_Petrochemicals_Sample_EU_NA_Apr_2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AE3B68-1B9D-482F-A9CB-873F60256474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F43BD36-195D-4E5C-A9BB-7D22240CA980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{49FED9BB-E9B4-4298-B606-A2033C4439F2}"/>
+    <workbookView xWindow="-11760" yWindow="12864" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{49FED9BB-E9B4-4298-B606-A2033C4439F2}"/>
   </bookViews>
   <sheets>
     <sheet name="About - General" sheetId="2" r:id="rId1"/>
@@ -5041,14 +5041,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9008B2CA-3D0D-4C83-BA51-A4822FB11F35}">
   <dimension ref="A1:D54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" style="18" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" customWidth="1"/>
-    <col min="3" max="3" width="100.88671875" customWidth="1"/>
+    <col min="1" max="1" width="5.85546875" style="18" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" customWidth="1"/>
+    <col min="3" max="3" width="100.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="29"/>
       <c r="B1" s="31" t="s">
         <v>0</v>
@@ -5056,85 +5056,85 @@
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
     </row>
-    <row r="2" spans="1:4" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="6.4" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="33"/>
     </row>
-    <row r="4" spans="1:4" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
     </row>
-    <row r="5" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="33"/>
       <c r="C5" s="33"/>
     </row>
-    <row r="6" spans="1:4" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15"/>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
     </row>
-    <row r="7" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="32"/>
       <c r="C7" s="32"/>
     </row>
-    <row r="8" spans="1:4" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19"/>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
         <v>1428</v>
       </c>
       <c r="B9" s="33"/>
       <c r="C9" s="33"/>
     </row>
-    <row r="10" spans="1:4" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19"/>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
         <v>1427</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="32"/>
     </row>
-    <row r="12" spans="1:4" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
     </row>
-    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="32" t="s">
         <v>4</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="32"/>
     </row>
-    <row r="14" spans="1:4" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
     </row>
-    <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>1</v>
       </c>
@@ -5145,7 +5145,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <v>2</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <v>3</v>
       </c>
@@ -5167,7 +5167,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <v>4</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <v>5</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <v>6</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <v>7</v>
       </c>
@@ -5211,7 +5211,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <v>8</v>
       </c>
@@ -5222,7 +5222,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <v>9</v>
       </c>
@@ -5233,7 +5233,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <v>10</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <v>11</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <v>12</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="17">
         <v>13</v>
       </c>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="17">
         <v>14</v>
       </c>
@@ -5288,7 +5288,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="17">
         <v>15</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="17">
         <v>16</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="17">
         <v>17</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="17">
         <v>18</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="17">
         <v>19</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="17">
         <v>20</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="17">
         <v>21</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="17">
         <v>22</v>
       </c>
@@ -5376,7 +5376,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="17">
         <v>23</v>
       </c>
@@ -5387,7 +5387,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="17">
         <v>24</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="17">
         <v>25</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="17">
         <v>26</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="17">
         <v>27</v>
       </c>
@@ -5431,7 +5431,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="17">
         <v>28</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="17">
         <v>29</v>
       </c>
@@ -5453,7 +5453,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="17">
         <v>30</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="17">
         <v>31</v>
       </c>
@@ -5475,7 +5475,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="17">
         <v>32</v>
       </c>
@@ -5486,7 +5486,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="17">
         <v>33</v>
       </c>
@@ -5497,7 +5497,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="17">
         <v>34</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="17">
         <v>35</v>
       </c>
@@ -5519,14 +5519,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="33" t="s">
         <v>76</v>
       </c>
       <c r="B53" s="33"/>
       <c r="C53" s="33"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
         <v>77</v>
       </c>
@@ -5551,19 +5551,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0D36391-A4E2-4B2A-AAD1-7B3B07126157}">
   <dimension ref="A2:I28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="30.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>78</v>
       </c>
@@ -5576,12 +5576,12 @@
       <c r="H2" s="34"/>
       <c r="I2" s="34"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
         <v>80</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
         <v>89</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>1.0478950617283951</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>90</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>0.66127963285024149</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
         <v>91</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>0.42632098765432097</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>92</v>
       </c>
@@ -5726,7 +5726,7 @@
         <v>0.29035215743440229</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
         <v>93</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>0.43076923076923079</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>94</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>0.76014999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="25" t="s">
         <v>95</v>
       </c>
@@ -5813,7 +5813,7 @@
         <v>0.9868055555555556</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
         <v>96</v>
       </c>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="I14" s="27"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C15" s="23">
         <v>0.62790697674418605</v>
       </c>
@@ -5852,12 +5852,12 @@
         <v>0.76663468337252794</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="30" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
         <v>80</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>89</v>
       </c>
@@ -5915,7 +5915,7 @@
         <v>1.0104962025316455</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>90</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>0.25263157894736843</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>91</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>0.92666666666666664</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
         <v>92</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>0.46149789029535865</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
         <v>93</v>
       </c>
@@ -6031,7 +6031,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>94</v>
       </c>
@@ -6060,7 +6060,7 @@
         <v>0.96381583333333343</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
         <v>95</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>0.98919374999999987</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
         <v>96</v>
       </c>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="I27" s="27"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C28" s="23">
         <v>0.46</v>
       </c>
@@ -6141,42 +6141,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D0948F-DE93-4FDE-A3AE-2B5CEA80AE20}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AK296"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="15.109375" customWidth="1"/>
+    <col min="2" max="3" width="15.140625" customWidth="1"/>
     <col min="4" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="24.5546875" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" customWidth="1"/>
-    <col min="10" max="10" width="31.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="10" max="10" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
-    <col min="15" max="15" width="16.5546875" customWidth="1"/>
+    <col min="15" max="15" width="16.5703125" customWidth="1"/>
     <col min="16" max="16" width="10" customWidth="1"/>
     <col min="17" max="17" width="16" customWidth="1"/>
-    <col min="18" max="19" width="10.33203125" customWidth="1"/>
-    <col min="20" max="20" width="16.5546875" customWidth="1"/>
-    <col min="21" max="21" width="47.88671875" customWidth="1"/>
-    <col min="22" max="22" width="13.33203125" customWidth="1"/>
-    <col min="23" max="23" width="14.109375" customWidth="1"/>
-    <col min="24" max="24" width="16.5546875" customWidth="1"/>
-    <col min="25" max="25" width="47.88671875" customWidth="1"/>
-    <col min="26" max="26" width="17.88671875" customWidth="1"/>
+    <col min="18" max="19" width="10.28515625" customWidth="1"/>
+    <col min="20" max="20" width="16.5703125" customWidth="1"/>
+    <col min="21" max="21" width="47.85546875" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" customWidth="1"/>
+    <col min="24" max="24" width="16.5703125" customWidth="1"/>
+    <col min="25" max="25" width="47.85546875" customWidth="1"/>
+    <col min="26" max="26" width="17.85546875" customWidth="1"/>
     <col min="27" max="27" width="25" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.5546875" customWidth="1"/>
-    <col min="32" max="32" width="47.88671875" customWidth="1"/>
-    <col min="33" max="33" width="17.88671875" customWidth="1"/>
-    <col min="34" max="34" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.5703125" customWidth="1"/>
+    <col min="32" max="32" width="47.85546875" customWidth="1"/>
+    <col min="33" max="33" width="17.85546875" customWidth="1"/>
+    <col min="34" max="34" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="15" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>1429</v>
       </c>
@@ -6289,7 +6289,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>99</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>120</v>
       </c>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AG3" s="9"/>
     </row>
-    <row r="4" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>128</v>
       </c>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="AG4" s="9"/>
     </row>
-    <row r="5" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>129</v>
       </c>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="AG5" s="9"/>
     </row>
-    <row r="6" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>1185</v>
       </c>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="AG6" s="9"/>
     </row>
-    <row r="7" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>1194</v>
       </c>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AG7" s="9"/>
     </row>
-    <row r="8" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>1430</v>
       </c>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="AG8" s="9"/>
     </row>
-    <row r="9" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>1430</v>
       </c>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="AG9" s="9"/>
     </row>
-    <row r="10" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>1430</v>
       </c>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="AG10" s="9"/>
     </row>
-    <row r="11" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>1430</v>
       </c>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="AG11" s="9"/>
     </row>
-    <row r="12" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>1430</v>
       </c>
@@ -7252,7 +7252,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>1430</v>
       </c>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AG13" s="9"/>
     </row>
-    <row r="14" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>1431</v>
       </c>
@@ -7431,7 +7431,7 @@
       </c>
       <c r="AG14" s="9"/>
     </row>
-    <row r="15" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>170</v>
       </c>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="AG15" s="9"/>
     </row>
-    <row r="16" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
         <v>182</v>
       </c>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="AG16" s="9"/>
     </row>
-    <row r="17" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
         <v>193</v>
       </c>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="AG17" s="9"/>
     </row>
-    <row r="18" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>298</v>
       </c>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="AG18" s="9"/>
     </row>
-    <row r="19" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
         <v>309</v>
       </c>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AG19" s="9"/>
     </row>
-    <row r="20" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
         <v>320</v>
       </c>
@@ -7943,7 +7943,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="21" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
         <v>327</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
         <v>328</v>
       </c>
@@ -8136,7 +8136,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
         <v>329</v>
       </c>
@@ -8231,7 +8231,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
         <v>330</v>
       </c>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="AG24" s="9"/>
     </row>
-    <row r="25" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
         <v>342</v>
       </c>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="AG25" s="9"/>
     </row>
-    <row r="26" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>349</v>
       </c>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="AG26" s="9"/>
     </row>
-    <row r="27" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>358</v>
       </c>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="AG27" s="9"/>
     </row>
-    <row r="28" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>359</v>
       </c>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="AG28" s="9"/>
     </row>
-    <row r="29" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>360</v>
       </c>
@@ -8737,7 +8737,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="30" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
         <v>366</v>
       </c>
@@ -8838,7 +8838,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="31" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
         <v>370</v>
       </c>
@@ -8936,7 +8936,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
         <v>376</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
         <v>382</v>
       </c>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="AG33" s="9"/>
     </row>
-    <row r="34" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
         <v>388</v>
       </c>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="AG34" s="9"/>
     </row>
-    <row r="35" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
         <v>392</v>
       </c>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AG35" s="9"/>
     </row>
-    <row r="36" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="s">
         <v>396</v>
       </c>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AG36" s="9"/>
     </row>
-    <row r="37" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
         <v>404</v>
       </c>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="AG37" s="9"/>
     </row>
-    <row r="38" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B38" s="6" t="s">
         <v>405</v>
       </c>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="AG38" s="9"/>
     </row>
-    <row r="39" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
         <v>406</v>
       </c>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="AG39" s="9"/>
     </row>
-    <row r="40" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
         <v>407</v>
       </c>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="AG40" s="9"/>
     </row>
-    <row r="41" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>1432</v>
       </c>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AG41" s="9"/>
     </row>
-    <row r="42" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>1432</v>
       </c>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="AG42" s="9"/>
     </row>
-    <row r="43" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>1432</v>
       </c>
@@ -9961,7 +9961,7 @@
       </c>
       <c r="AG43" s="9"/>
     </row>
-    <row r="44" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>1432</v>
       </c>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AG44" s="9"/>
     </row>
-    <row r="45" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B45" s="6" t="s">
         <v>423</v>
       </c>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="AG45" s="9"/>
     </row>
-    <row r="46" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>1432</v>
       </c>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AG46" s="9"/>
     </row>
-    <row r="47" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>1432</v>
       </c>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="AG47" s="9"/>
     </row>
-    <row r="48" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>1432</v>
       </c>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="AG48" s="9"/>
     </row>
-    <row r="49" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>1432</v>
       </c>
@@ -10425,7 +10425,7 @@
       </c>
       <c r="AG49" s="9"/>
     </row>
-    <row r="50" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>1432</v>
       </c>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="AG50" s="9"/>
     </row>
-    <row r="51" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B51" s="6" t="s">
         <v>439</v>
       </c>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="AG51" s="9"/>
     </row>
-    <row r="52" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
         <v>447</v>
       </c>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="AG52" s="9"/>
     </row>
-    <row r="53" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B53" s="6" t="s">
         <v>453</v>
       </c>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="AG53" s="9"/>
     </row>
-    <row r="54" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>1432</v>
       </c>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AG54" s="9"/>
     </row>
-    <row r="55" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>1432</v>
       </c>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="AG55" s="9"/>
     </row>
-    <row r="56" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>1432</v>
       </c>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="AG56" s="9"/>
     </row>
-    <row r="57" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B57" s="6" t="s">
         <v>459</v>
       </c>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="AG57" s="9"/>
     </row>
-    <row r="58" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B58" s="6" t="s">
         <v>464</v>
       </c>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AG58" s="9"/>
     </row>
-    <row r="59" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B59" s="6" t="s">
         <v>465</v>
       </c>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="AG59" s="9"/>
     </row>
-    <row r="60" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B60" s="6" t="s">
         <v>466</v>
       </c>
@@ -11342,7 +11342,7 @@
       </c>
       <c r="AG60" s="9"/>
     </row>
-    <row r="61" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B61" s="6" t="s">
         <v>467</v>
       </c>
@@ -11443,7 +11443,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B62" s="6" t="s">
         <v>476</v>
       </c>
@@ -11539,7 +11539,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="63" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B63" s="6" t="s">
         <v>483</v>
       </c>
@@ -11635,7 +11635,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="64" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B64" s="6" t="s">
         <v>484</v>
       </c>
@@ -11731,7 +11731,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="65" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>1432</v>
       </c>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="AG65" s="9"/>
     </row>
-    <row r="66" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>1432</v>
       </c>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="AG66" s="9"/>
     </row>
-    <row r="67" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>1432</v>
       </c>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="AG67" s="9"/>
     </row>
-    <row r="68" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>1432</v>
       </c>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="AG68" s="9"/>
     </row>
-    <row r="69" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>1432</v>
       </c>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="AG69" s="9"/>
     </row>
-    <row r="70" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>1432</v>
       </c>
@@ -12234,7 +12234,7 @@
       </c>
       <c r="AG70" s="9"/>
     </row>
-    <row r="71" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>1432</v>
       </c>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="AG71" s="9"/>
     </row>
-    <row r="72" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B72" s="6" t="s">
         <v>497</v>
       </c>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="AG72" s="9"/>
     </row>
-    <row r="73" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B73" s="6" t="s">
         <v>502</v>
       </c>
@@ -12484,7 +12484,7 @@
       </c>
       <c r="AG73" s="9"/>
     </row>
-    <row r="74" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B74" s="6" t="s">
         <v>513</v>
       </c>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="AG74" s="9"/>
     </row>
-    <row r="75" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B75" s="6" t="s">
         <v>514</v>
       </c>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="AG75" s="9"/>
     </row>
-    <row r="76" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B76" s="6" t="s">
         <v>521</v>
       </c>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="AG76" s="9"/>
     </row>
-    <row r="77" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B77" s="6" t="s">
         <v>528</v>
       </c>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="AG77" s="9"/>
     </row>
-    <row r="78" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B78" s="6" t="s">
         <v>532</v>
       </c>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="AG78" s="9"/>
     </row>
-    <row r="79" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B79" s="6" t="s">
         <v>536</v>
       </c>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="AG79" s="9"/>
     </row>
-    <row r="80" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B80" s="6" t="s">
         <v>542</v>
       </c>
@@ -13044,7 +13044,7 @@
       </c>
       <c r="AG80" s="9"/>
     </row>
-    <row r="81" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B81" s="6" t="s">
         <v>552</v>
       </c>
@@ -13126,7 +13126,7 @@
       </c>
       <c r="AG81" s="9"/>
     </row>
-    <row r="82" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
         <v>1433</v>
       </c>
@@ -13212,7 +13212,7 @@
       </c>
       <c r="AG82" s="9"/>
     </row>
-    <row r="83" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
         <v>1433</v>
       </c>
@@ -13298,7 +13298,7 @@
       </c>
       <c r="AG83" s="9"/>
     </row>
-    <row r="84" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
         <v>1433</v>
       </c>
@@ -13384,7 +13384,7 @@
       </c>
       <c r="AG84" s="9"/>
     </row>
-    <row r="85" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
         <v>1433</v>
       </c>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="AG85" s="9"/>
     </row>
-    <row r="86" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
         <v>1435</v>
       </c>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="AG86" s="9"/>
     </row>
-    <row r="87" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>1433</v>
       </c>
@@ -13637,7 +13637,7 @@
       </c>
       <c r="AG87" s="9"/>
     </row>
-    <row r="88" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
         <v>1433</v>
       </c>
@@ -13725,7 +13725,7 @@
       </c>
       <c r="AG88" s="9"/>
     </row>
-    <row r="89" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
         <v>1433</v>
       </c>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="AG89" s="9"/>
     </row>
-    <row r="90" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
         <v>1433</v>
       </c>
@@ -13901,7 +13901,7 @@
       </c>
       <c r="AG90" s="9"/>
     </row>
-    <row r="91" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
         <v>1433</v>
       </c>
@@ -13992,7 +13992,7 @@
       </c>
       <c r="AG91" s="9"/>
     </row>
-    <row r="92" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
         <v>1434</v>
       </c>
@@ -14080,7 +14080,7 @@
       </c>
       <c r="AG92" s="9"/>
     </row>
-    <row r="93" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
         <v>1434</v>
       </c>
@@ -14168,7 +14168,7 @@
       </c>
       <c r="AG93" s="9"/>
     </row>
-    <row r="94" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
         <v>1434</v>
       </c>
@@ -14251,7 +14251,7 @@
       </c>
       <c r="AG94" s="9"/>
     </row>
-    <row r="95" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
         <v>1434</v>
       </c>
@@ -14334,7 +14334,7 @@
       </c>
       <c r="AG95" s="9"/>
     </row>
-    <row r="96" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
         <v>1433</v>
       </c>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="AG96" s="9"/>
     </row>
-    <row r="97" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B97" s="6" t="s">
         <v>1196</v>
       </c>
@@ -14535,7 +14535,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="98" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B98" s="6" t="s">
         <v>1209</v>
       </c>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="AG98" s="9"/>
     </row>
-    <row r="99" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B99" s="6" t="s">
         <v>1216</v>
       </c>
@@ -14693,7 +14693,7 @@
       </c>
       <c r="AG99" s="9"/>
     </row>
-    <row r="100" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B100" s="6" t="s">
         <v>1218</v>
       </c>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="AG100" s="9"/>
     </row>
-    <row r="101" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B101" s="6" t="s">
         <v>606</v>
       </c>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="AG101" s="9"/>
     </row>
-    <row r="102" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B102" s="6" t="s">
         <v>617</v>
       </c>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="AG102" s="9"/>
     </row>
-    <row r="103" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B103" s="6" t="s">
         <v>623</v>
       </c>
@@ -15021,7 +15021,7 @@
       </c>
       <c r="AG103" s="9"/>
     </row>
-    <row r="104" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B104" s="6" t="s">
         <v>632</v>
       </c>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="AG104" s="9"/>
     </row>
-    <row r="105" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B105" s="6" t="s">
         <v>643</v>
       </c>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="AG105" s="9"/>
     </row>
-    <row r="106" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B106" s="6" t="s">
         <v>649</v>
       </c>
@@ -15271,7 +15271,7 @@
       </c>
       <c r="AG106" s="9"/>
     </row>
-    <row r="107" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B107" s="6" t="s">
         <v>650</v>
       </c>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="AG107" s="9"/>
     </row>
-    <row r="108" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B108" s="6" t="s">
         <v>657</v>
       </c>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="AG108" s="9"/>
     </row>
-    <row r="109" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B109" s="6" t="s">
         <v>1223</v>
       </c>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="AG109" s="9"/>
     </row>
-    <row r="110" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B110" s="6" t="s">
         <v>1234</v>
       </c>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="AG110" s="9"/>
     </row>
-    <row r="111" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B111" s="6" t="s">
         <v>1236</v>
       </c>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AG111" s="9"/>
     </row>
-    <row r="112" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B112" s="6" t="s">
         <v>1241</v>
       </c>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AG112" s="9"/>
     </row>
-    <row r="113" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B113" s="6" t="s">
         <v>1242</v>
       </c>
@@ -15814,7 +15814,7 @@
       </c>
       <c r="AG113" s="9"/>
     </row>
-    <row r="114" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B114" s="6" t="s">
         <v>1248</v>
       </c>
@@ -15899,7 +15899,7 @@
       </c>
       <c r="AG114" s="9"/>
     </row>
-    <row r="115" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B115" s="6" t="s">
         <v>1257</v>
       </c>
@@ -15975,7 +15975,7 @@
       </c>
       <c r="AG115" s="9"/>
     </row>
-    <row r="116" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B116" s="6" t="s">
         <v>1263</v>
       </c>
@@ -16051,7 +16051,7 @@
       </c>
       <c r="AG116" s="9"/>
     </row>
-    <row r="117" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B117" s="6" t="s">
         <v>1264</v>
       </c>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="AG117" s="9"/>
     </row>
-    <row r="118" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B118" s="6" t="s">
         <v>1272</v>
       </c>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="AG118" s="9"/>
     </row>
-    <row r="119" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B119" s="6" t="s">
         <v>1273</v>
       </c>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="AG119" s="9"/>
     </row>
-    <row r="120" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B120" s="6" t="s">
         <v>1280</v>
       </c>
@@ -16373,7 +16373,7 @@
       </c>
       <c r="AG120" s="9"/>
     </row>
-    <row r="121" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B121" s="6" t="s">
         <v>1287</v>
       </c>
@@ -16452,7 +16452,7 @@
       </c>
       <c r="AG121" s="9"/>
     </row>
-    <row r="122" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B122" s="6" t="s">
         <v>1288</v>
       </c>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="AG122" s="9"/>
     </row>
-    <row r="123" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B123" s="6" t="s">
         <v>1289</v>
       </c>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="AG123" s="9"/>
     </row>
-    <row r="124" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B124" s="6" t="s">
         <v>1295</v>
       </c>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="AG124" s="9"/>
     </row>
-    <row r="125" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B125" s="6" t="s">
         <v>1302</v>
       </c>
@@ -16780,7 +16780,7 @@
       </c>
       <c r="AG125" s="9"/>
     </row>
-    <row r="126" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B126" s="6" t="s">
         <v>1303</v>
       </c>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="AG126" s="9"/>
     </row>
-    <row r="127" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B127" s="6" t="s">
         <v>1304</v>
       </c>
@@ -16944,7 +16944,7 @@
       </c>
       <c r="AG127" s="9"/>
     </row>
-    <row r="128" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B128" s="6" t="s">
         <v>1305</v>
       </c>
@@ -17020,7 +17020,7 @@
       </c>
       <c r="AG128" s="9"/>
     </row>
-    <row r="129" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B129" s="6" t="s">
         <v>1311</v>
       </c>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="AG129" s="9"/>
     </row>
-    <row r="130" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B130" s="6" t="s">
         <v>1312</v>
       </c>
@@ -17171,7 +17171,7 @@
       </c>
       <c r="AG130" s="9"/>
     </row>
-    <row r="131" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B131" s="6" t="s">
         <v>1321</v>
       </c>
@@ -17251,7 +17251,7 @@
       </c>
       <c r="AG131" s="9"/>
     </row>
-    <row r="132" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B132" s="6" t="s">
         <v>1322</v>
       </c>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="AG132" s="9"/>
     </row>
-    <row r="133" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B133" s="6" t="s">
         <v>1323</v>
       </c>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="AG133" s="9"/>
     </row>
-    <row r="134" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B134" s="6" t="s">
         <v>1331</v>
       </c>
@@ -17483,7 +17483,7 @@
       </c>
       <c r="AG134" s="9"/>
     </row>
-    <row r="135" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B135" s="6" t="s">
         <v>1332</v>
       </c>
@@ -17559,7 +17559,7 @@
       </c>
       <c r="AG135" s="9"/>
     </row>
-    <row r="136" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B136" s="6" t="s">
         <v>1333</v>
       </c>
@@ -17633,7 +17633,7 @@
       </c>
       <c r="AG136" s="9"/>
     </row>
-    <row r="137" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B137" s="6" t="s">
         <v>1335</v>
       </c>
@@ -17707,7 +17707,7 @@
       </c>
       <c r="AG137" s="9"/>
     </row>
-    <row r="138" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B138" s="6" t="s">
         <v>1336</v>
       </c>
@@ -17786,7 +17786,7 @@
       </c>
       <c r="AG138" s="9"/>
     </row>
-    <row r="139" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B139" s="6" t="s">
         <v>1343</v>
       </c>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="AG139" s="9"/>
     </row>
-    <row r="140" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B140" s="6" t="s">
         <v>1344</v>
       </c>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="AG140" s="9"/>
     </row>
-    <row r="141" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B141" s="6" t="s">
         <v>1345</v>
       </c>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="AG141" s="9"/>
     </row>
-    <row r="142" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B142" s="6" t="s">
         <v>1352</v>
       </c>
@@ -18103,7 +18103,7 @@
       </c>
       <c r="AG142" s="9"/>
     </row>
-    <row r="143" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B143" s="6" t="s">
         <v>1357</v>
       </c>
@@ -18174,7 +18174,7 @@
       </c>
       <c r="AG143" s="9"/>
     </row>
-    <row r="144" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B144" s="6" t="s">
         <v>1362</v>
       </c>
@@ -18256,7 +18256,7 @@
       </c>
       <c r="AG144" s="9"/>
     </row>
-    <row r="145" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B145" s="6" t="s">
         <v>1372</v>
       </c>
@@ -18335,7 +18335,7 @@
       </c>
       <c r="AG145" s="9"/>
     </row>
-    <row r="146" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B146" s="6" t="s">
         <v>665</v>
       </c>
@@ -18415,7 +18415,7 @@
       </c>
       <c r="AG146" s="9"/>
     </row>
-    <row r="147" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B147" s="6" t="s">
         <v>673</v>
       </c>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="AG147" s="9"/>
     </row>
-    <row r="148" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B148" s="6" t="s">
         <v>681</v>
       </c>
@@ -18595,7 +18595,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="149" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B149" s="6" t="s">
         <v>690</v>
       </c>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="AG149" s="9"/>
     </row>
-    <row r="150" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B150" s="6" t="s">
         <v>694</v>
       </c>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="AG150" s="9"/>
     </row>
-    <row r="151" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B151" s="6" t="s">
         <v>699</v>
       </c>
@@ -18838,7 +18838,7 @@
       </c>
       <c r="AG151" s="9"/>
     </row>
-    <row r="152" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B152" s="6" t="s">
         <v>704</v>
       </c>
@@ -18920,7 +18920,7 @@
       </c>
       <c r="AG152" s="9"/>
     </row>
-    <row r="153" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B153" s="6" t="s">
         <v>712</v>
       </c>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="AG153" s="9"/>
     </row>
-    <row r="154" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B154" s="6" t="s">
         <v>714</v>
       </c>
@@ -19103,7 +19103,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="155" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B155" s="6" t="s">
         <v>722</v>
       </c>
@@ -19204,7 +19204,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="156" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B156" s="6" t="s">
         <v>1379</v>
       </c>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="AG156" s="9"/>
     </row>
-    <row r="157" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B157" s="6" t="s">
         <v>1391</v>
       </c>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="AG157" s="9"/>
     </row>
-    <row r="158" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B158" s="6" t="s">
         <v>1399</v>
       </c>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="AG158" s="9"/>
     </row>
-    <row r="159" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B159" s="6" t="s">
         <v>1405</v>
       </c>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="AG159" s="9"/>
     </row>
-    <row r="160" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:35" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B160" s="6" t="s">
         <v>1406</v>
       </c>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="AG160" s="9"/>
     </row>
-    <row r="161" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B161" s="6" t="s">
         <v>1412</v>
       </c>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="AG161" s="9"/>
     </row>
-    <row r="162" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B162" s="6" t="s">
         <v>1418</v>
       </c>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="AG162" s="9"/>
     </row>
-    <row r="163" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B163" s="6" t="s">
         <v>1425</v>
       </c>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="AG163" s="9"/>
     </row>
-    <row r="164" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B164" s="6" t="s">
         <v>1426</v>
       </c>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="AG164" s="9"/>
     </row>
-    <row r="165" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B165" s="6" t="s">
         <v>723</v>
       </c>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="AG165" s="9"/>
     </row>
-    <row r="166" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B166" s="6" t="s">
         <v>731</v>
       </c>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="AG166" s="9"/>
     </row>
-    <row r="167" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B167" s="6" t="s">
         <v>736</v>
       </c>
@@ -20201,7 +20201,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="168" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B168" s="6" t="s">
         <v>743</v>
       </c>
@@ -20272,7 +20272,7 @@
       </c>
       <c r="AG168" s="9"/>
     </row>
-    <row r="169" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B169" s="6" t="s">
         <v>749</v>
       </c>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="AG169" s="9"/>
     </row>
-    <row r="170" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B170" s="6" t="s">
         <v>750</v>
       </c>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="AG170" s="9"/>
     </row>
-    <row r="171" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B171" s="6" t="s">
         <v>757</v>
       </c>
@@ -20519,7 +20519,7 @@
       </c>
       <c r="AG171" s="9"/>
     </row>
-    <row r="172" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B172" s="6" t="s">
         <v>758</v>
       </c>
@@ -20602,7 +20602,7 @@
       </c>
       <c r="AG172" s="9"/>
     </row>
-    <row r="173" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B173" s="6" t="s">
         <v>759</v>
       </c>
@@ -20687,7 +20687,7 @@
       </c>
       <c r="AG173" s="9"/>
     </row>
-    <row r="174" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B174" s="6" t="s">
         <v>194</v>
       </c>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="AG174" s="9"/>
     </row>
-    <row r="175" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B175" s="6" t="s">
         <v>209</v>
       </c>
@@ -20857,7 +20857,7 @@
       </c>
       <c r="AG175" s="9"/>
     </row>
-    <row r="176" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B176" s="6" t="s">
         <v>214</v>
       </c>
@@ -20942,7 +20942,7 @@
       </c>
       <c r="AG176" s="9"/>
     </row>
-    <row r="177" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B177" s="6" t="s">
         <v>223</v>
       </c>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="AG177" s="9"/>
     </row>
-    <row r="178" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B178" s="6" t="s">
         <v>231</v>
       </c>
@@ -21112,7 +21112,7 @@
       </c>
       <c r="AG178" s="9"/>
     </row>
-    <row r="179" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B179" s="6" t="s">
         <v>237</v>
       </c>
@@ -21197,7 +21197,7 @@
       </c>
       <c r="AG179" s="9"/>
     </row>
-    <row r="180" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B180" s="6" t="s">
         <v>238</v>
       </c>
@@ -21282,7 +21282,7 @@
       </c>
       <c r="AG180" s="9"/>
     </row>
-    <row r="181" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B181" s="6" t="s">
         <v>243</v>
       </c>
@@ -21367,7 +21367,7 @@
       </c>
       <c r="AG181" s="9"/>
     </row>
-    <row r="182" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B182" s="6" t="s">
         <v>251</v>
       </c>
@@ -21452,7 +21452,7 @@
       </c>
       <c r="AG182" s="9"/>
     </row>
-    <row r="183" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B183" s="6" t="s">
         <v>253</v>
       </c>
@@ -21537,7 +21537,7 @@
       </c>
       <c r="AG183" s="9"/>
     </row>
-    <row r="184" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B184" s="6" t="s">
         <v>255</v>
       </c>
@@ -21622,7 +21622,7 @@
       </c>
       <c r="AG184" s="9"/>
     </row>
-    <row r="185" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B185" s="6" t="s">
         <v>257</v>
       </c>
@@ -21707,7 +21707,7 @@
       </c>
       <c r="AG185" s="9"/>
     </row>
-    <row r="186" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B186" s="6" t="s">
         <v>265</v>
       </c>
@@ -21787,7 +21787,7 @@
       </c>
       <c r="AG186" s="9"/>
     </row>
-    <row r="187" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B187" s="6" t="s">
         <v>267</v>
       </c>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="AG187" s="9"/>
     </row>
-    <row r="188" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B188" s="6" t="s">
         <v>268</v>
       </c>
@@ -21957,7 +21957,7 @@
       </c>
       <c r="AG188" s="9"/>
     </row>
-    <row r="189" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B189" s="6" t="s">
         <v>269</v>
       </c>
@@ -22045,7 +22045,7 @@
       </c>
       <c r="AG189" s="9"/>
     </row>
-    <row r="190" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B190" s="6" t="s">
         <v>275</v>
       </c>
@@ -22130,7 +22130,7 @@
       </c>
       <c r="AG190" s="9"/>
     </row>
-    <row r="191" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B191" s="6" t="s">
         <v>283</v>
       </c>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="AG191" s="9"/>
     </row>
-    <row r="192" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B192" s="6" t="s">
         <v>284</v>
       </c>
@@ -22300,7 +22300,7 @@
       </c>
       <c r="AG192" s="9"/>
     </row>
-    <row r="193" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B193" s="6" t="s">
         <v>285</v>
       </c>
@@ -22385,7 +22385,7 @@
       </c>
       <c r="AG193" s="9"/>
     </row>
-    <row r="194" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B194" s="6" t="s">
         <v>293</v>
       </c>
@@ -22470,7 +22470,7 @@
       </c>
       <c r="AG194" s="9"/>
     </row>
-    <row r="195" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B195" s="6" t="s">
         <v>294</v>
       </c>
@@ -22555,7 +22555,7 @@
       </c>
       <c r="AG195" s="9"/>
     </row>
-    <row r="196" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B196" s="6" t="s">
         <v>297</v>
       </c>
@@ -22640,7 +22640,7 @@
       </c>
       <c r="AG196" s="9"/>
     </row>
-    <row r="197" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B197" s="6" t="s">
         <v>765</v>
       </c>
@@ -22720,7 +22720,7 @@
       </c>
       <c r="AG197" s="9"/>
     </row>
-    <row r="198" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B198" s="6" t="s">
         <v>775</v>
       </c>
@@ -22794,7 +22794,7 @@
       </c>
       <c r="AG198" s="9"/>
     </row>
-    <row r="199" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B199" s="6" t="s">
         <v>783</v>
       </c>
@@ -22904,7 +22904,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="200" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B200" s="6" t="s">
         <v>788</v>
       </c>
@@ -23008,7 +23008,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="201" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B201" s="6" t="s">
         <v>791</v>
       </c>
@@ -23112,7 +23112,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="202" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B202" s="6" t="s">
         <v>792</v>
       </c>
@@ -23216,7 +23216,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="203" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B203" s="6" t="s">
         <v>793</v>
       </c>
@@ -23290,7 +23290,7 @@
       </c>
       <c r="AG203" s="9"/>
     </row>
-    <row r="204" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B204" s="6" t="s">
         <v>801</v>
       </c>
@@ -23375,7 +23375,7 @@
       </c>
       <c r="AG204" s="9"/>
     </row>
-    <row r="205" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B205" s="6" t="s">
         <v>806</v>
       </c>
@@ -23460,7 +23460,7 @@
       </c>
       <c r="AG205" s="9"/>
     </row>
-    <row r="206" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B206" s="6" t="s">
         <v>811</v>
       </c>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="AG206" s="9"/>
     </row>
-    <row r="207" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B207" s="6" t="s">
         <v>816</v>
       </c>
@@ -23630,7 +23630,7 @@
       </c>
       <c r="AG207" s="9"/>
     </row>
-    <row r="208" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B208" s="6" t="s">
         <v>820</v>
       </c>
@@ -23715,7 +23715,7 @@
       </c>
       <c r="AG208" s="9"/>
     </row>
-    <row r="209" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B209" s="6" t="s">
         <v>825</v>
       </c>
@@ -23789,7 +23789,7 @@
       </c>
       <c r="AG209" s="9"/>
     </row>
-    <row r="210" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B210" s="6" t="s">
         <v>831</v>
       </c>
@@ -23863,7 +23863,7 @@
       </c>
       <c r="AG210" s="9"/>
     </row>
-    <row r="211" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B211" s="6" t="s">
         <v>832</v>
       </c>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="AG211" s="9"/>
     </row>
-    <row r="212" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B212" s="6" t="s">
         <v>837</v>
       </c>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="AG212" s="9"/>
     </row>
-    <row r="213" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B213" s="6" t="s">
         <v>840</v>
       </c>
@@ -24090,7 +24090,7 @@
       </c>
       <c r="AG213" s="9"/>
     </row>
-    <row r="214" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B214" s="6" t="s">
         <v>841</v>
       </c>
@@ -24175,7 +24175,7 @@
       </c>
       <c r="AG214" s="9"/>
     </row>
-    <row r="215" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B215" s="6" t="s">
         <v>850</v>
       </c>
@@ -24260,7 +24260,7 @@
       </c>
       <c r="AG215" s="9"/>
     </row>
-    <row r="216" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B216" s="6" t="s">
         <v>855</v>
       </c>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="AG216" s="9"/>
     </row>
-    <row r="217" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B217" s="6" t="s">
         <v>860</v>
       </c>
@@ -24420,7 +24420,7 @@
       </c>
       <c r="AG217" s="9"/>
     </row>
-    <row r="218" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B218" s="6" t="s">
         <v>864</v>
       </c>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="AG218" s="9"/>
     </row>
-    <row r="219" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B219" s="6" t="s">
         <v>868</v>
       </c>
@@ -24583,7 +24583,7 @@
       </c>
       <c r="AG219" s="9"/>
     </row>
-    <row r="220" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B220" s="6" t="s">
         <v>871</v>
       </c>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="AG220" s="9"/>
     </row>
-    <row r="221" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B221" s="6" t="s">
         <v>878</v>
       </c>
@@ -24748,7 +24748,7 @@
       </c>
       <c r="AG221" s="9"/>
     </row>
-    <row r="222" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B222" s="6" t="s">
         <v>882</v>
       </c>
@@ -24828,7 +24828,7 @@
       </c>
       <c r="AG222" s="9"/>
     </row>
-    <row r="223" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B223" s="6" t="s">
         <v>883</v>
       </c>
@@ -24908,7 +24908,7 @@
       </c>
       <c r="AG223" s="9"/>
     </row>
-    <row r="224" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B224" s="6" t="s">
         <v>884</v>
       </c>
@@ -24988,7 +24988,7 @@
       </c>
       <c r="AG224" s="9"/>
     </row>
-    <row r="225" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B225" s="6" t="s">
         <v>885</v>
       </c>
@@ -25068,7 +25068,7 @@
       </c>
       <c r="AG225" s="9"/>
     </row>
-    <row r="226" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B226" s="6" t="s">
         <v>886</v>
       </c>
@@ -25153,7 +25153,7 @@
       </c>
       <c r="AG226" s="9"/>
     </row>
-    <row r="227" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B227" s="6" t="s">
         <v>890</v>
       </c>
@@ -25233,7 +25233,7 @@
       </c>
       <c r="AG227" s="9"/>
     </row>
-    <row r="228" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B228" s="6" t="s">
         <v>891</v>
       </c>
@@ -25313,7 +25313,7 @@
       </c>
       <c r="AG228" s="9"/>
     </row>
-    <row r="229" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B229" s="6" t="s">
         <v>892</v>
       </c>
@@ -25398,7 +25398,7 @@
       </c>
       <c r="AG229" s="9"/>
     </row>
-    <row r="230" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B230" s="6" t="s">
         <v>896</v>
       </c>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="AG230" s="9"/>
     </row>
-    <row r="231" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B231" s="6" t="s">
         <v>905</v>
       </c>
@@ -25552,7 +25552,7 @@
       </c>
       <c r="AG231" s="9"/>
     </row>
-    <row r="232" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B232" s="6" t="s">
         <v>910</v>
       </c>
@@ -25640,7 +25640,7 @@
       </c>
       <c r="AG232" s="9"/>
     </row>
-    <row r="233" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B233" s="6" t="s">
         <v>920</v>
       </c>
@@ -25720,7 +25720,7 @@
       </c>
       <c r="AG233" s="9"/>
     </row>
-    <row r="234" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B234" s="6" t="s">
         <v>924</v>
       </c>
@@ -25800,7 +25800,7 @@
       </c>
       <c r="AG234" s="9"/>
     </row>
-    <row r="235" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B235" s="6" t="s">
         <v>928</v>
       </c>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="AG235" s="9"/>
     </row>
-    <row r="236" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B236" s="6" t="s">
         <v>936</v>
       </c>
@@ -25964,7 +25964,7 @@
       </c>
       <c r="AG236" s="9"/>
     </row>
-    <row r="237" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B237" s="6" t="s">
         <v>937</v>
       </c>
@@ -26035,7 +26035,7 @@
       </c>
       <c r="AG237" s="9"/>
     </row>
-    <row r="238" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B238" s="6" t="s">
         <v>942</v>
       </c>
@@ -26106,7 +26106,7 @@
       </c>
       <c r="AG238" s="9"/>
     </row>
-    <row r="239" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B239" s="6" t="s">
         <v>943</v>
       </c>
@@ -26177,7 +26177,7 @@
       </c>
       <c r="AG239" s="9"/>
     </row>
-    <row r="240" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B240" s="6" t="s">
         <v>944</v>
       </c>
@@ -26251,7 +26251,7 @@
       </c>
       <c r="AG240" s="9"/>
     </row>
-    <row r="241" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B241" s="6" t="s">
         <v>950</v>
       </c>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="AG241" s="9"/>
     </row>
-    <row r="242" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B242" s="6" t="s">
         <v>958</v>
       </c>
@@ -26405,7 +26405,7 @@
       </c>
       <c r="AG242" s="9"/>
     </row>
-    <row r="243" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B243" s="6" t="s">
         <v>963</v>
       </c>
@@ -26482,7 +26482,7 @@
       </c>
       <c r="AG243" s="9"/>
     </row>
-    <row r="244" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B244" s="6" t="s">
         <v>968</v>
       </c>
@@ -26559,7 +26559,7 @@
       </c>
       <c r="AG244" s="9"/>
     </row>
-    <row r="245" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B245" s="6" t="s">
         <v>973</v>
       </c>
@@ -26644,7 +26644,7 @@
       </c>
       <c r="AG245" s="9"/>
     </row>
-    <row r="246" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B246" s="6" t="s">
         <v>982</v>
       </c>
@@ -26729,7 +26729,7 @@
       </c>
       <c r="AG246" s="9"/>
     </row>
-    <row r="247" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B247" s="6" t="s">
         <v>987</v>
       </c>
@@ -26814,7 +26814,7 @@
       </c>
       <c r="AG247" s="9"/>
     </row>
-    <row r="248" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B248" s="6" t="s">
         <v>991</v>
       </c>
@@ -26897,7 +26897,7 @@
       </c>
       <c r="AG248" s="9"/>
     </row>
-    <row r="249" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B249" s="6" t="s">
         <v>996</v>
       </c>
@@ -26980,7 +26980,7 @@
       </c>
       <c r="AG249" s="9"/>
     </row>
-    <row r="250" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B250" s="6" t="s">
         <v>997</v>
       </c>
@@ -27063,7 +27063,7 @@
       </c>
       <c r="AG250" s="9"/>
     </row>
-    <row r="251" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B251" s="6" t="s">
         <v>1001</v>
       </c>
@@ -27146,7 +27146,7 @@
       </c>
       <c r="AG251" s="9"/>
     </row>
-    <row r="252" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B252" s="6" t="s">
         <v>1002</v>
       </c>
@@ -27226,7 +27226,7 @@
       </c>
       <c r="AG252" s="9"/>
     </row>
-    <row r="253" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B253" s="6" t="s">
         <v>1006</v>
       </c>
@@ -27306,7 +27306,7 @@
       </c>
       <c r="AG253" s="9"/>
     </row>
-    <row r="254" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B254" s="6" t="s">
         <v>1007</v>
       </c>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="AG254" s="9"/>
     </row>
-    <row r="255" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B255" s="6" t="s">
         <v>1008</v>
       </c>
@@ -27466,7 +27466,7 @@
       </c>
       <c r="AG255" s="9"/>
     </row>
-    <row r="256" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:33" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B256" s="6" t="s">
         <v>1009</v>
       </c>
@@ -27546,7 +27546,7 @@
       </c>
       <c r="AG256" s="9"/>
     </row>
-    <row r="257" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B257" s="6" t="s">
         <v>1010</v>
       </c>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="AG257" s="9"/>
     </row>
-    <row r="258" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B258" s="6" t="s">
         <v>1011</v>
       </c>
@@ -27709,7 +27709,7 @@
       </c>
       <c r="AG258" s="9"/>
     </row>
-    <row r="259" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B259" s="6" t="s">
         <v>1015</v>
       </c>
@@ -27792,7 +27792,7 @@
       </c>
       <c r="AG259" s="9"/>
     </row>
-    <row r="260" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B260" s="6" t="s">
         <v>1016</v>
       </c>
@@ -27875,7 +27875,7 @@
       </c>
       <c r="AG260" s="9"/>
     </row>
-    <row r="261" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B261" s="6" t="s">
         <v>1020</v>
       </c>
@@ -27958,7 +27958,7 @@
       </c>
       <c r="AG261" s="9"/>
     </row>
-    <row r="262" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B262" s="6" t="s">
         <v>1021</v>
       </c>
@@ -28043,7 +28043,7 @@
       </c>
       <c r="AG262" s="9"/>
     </row>
-    <row r="263" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B263" s="6" t="s">
         <v>1025</v>
       </c>
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AG263" s="9"/>
     </row>
-    <row r="264" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B264" s="6" t="s">
         <v>1032</v>
       </c>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="AG264" s="9"/>
     </row>
-    <row r="265" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B265" s="6" t="s">
         <v>1037</v>
       </c>
@@ -28306,7 +28306,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="266" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B266" s="6" t="s">
         <v>1042</v>
       </c>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="AG266" s="9"/>
     </row>
-    <row r="267" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B267" s="6" t="s">
         <v>1046</v>
       </c>
@@ -28476,7 +28476,7 @@
       </c>
       <c r="AG267" s="9"/>
     </row>
-    <row r="268" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B268" s="6" t="s">
         <v>1049</v>
       </c>
@@ -28561,7 +28561,7 @@
       </c>
       <c r="AG268" s="9"/>
     </row>
-    <row r="269" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B269" s="6" t="s">
         <v>1053</v>
       </c>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="AG269" s="9"/>
     </row>
-    <row r="270" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B270" s="6" t="s">
         <v>1057</v>
       </c>
@@ -28753,7 +28753,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="271" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B271" s="6" t="s">
         <v>1068</v>
       </c>
@@ -28833,7 +28833,7 @@
       </c>
       <c r="AG271" s="9"/>
     </row>
-    <row r="272" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B272" s="6" t="s">
         <v>1075</v>
       </c>
@@ -28909,7 +28909,7 @@
       </c>
       <c r="AG272" s="9"/>
     </row>
-    <row r="273" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B273" s="6" t="s">
         <v>1081</v>
       </c>
@@ -28985,7 +28985,7 @@
       </c>
       <c r="AG273" s="9"/>
     </row>
-    <row r="274" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B274" s="6" t="s">
         <v>1082</v>
       </c>
@@ -29095,7 +29095,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="275" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B275" s="6" t="s">
         <v>1086</v>
       </c>
@@ -29166,7 +29166,7 @@
       </c>
       <c r="AG275" s="9"/>
     </row>
-    <row r="276" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B276" s="6" t="s">
         <v>1090</v>
       </c>
@@ -29261,7 +29261,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="277" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B277" s="6" t="s">
         <v>1096</v>
       </c>
@@ -29340,7 +29340,7 @@
       </c>
       <c r="AG277" s="9"/>
     </row>
-    <row r="278" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B278" s="6" t="s">
         <v>1102</v>
       </c>
@@ -29428,7 +29428,7 @@
       </c>
       <c r="AG278" s="9"/>
     </row>
-    <row r="279" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B279" s="6" t="s">
         <v>1106</v>
       </c>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="AG279" s="9"/>
     </row>
-    <row r="280" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B280" s="6" t="s">
         <v>1107</v>
       </c>
@@ -29599,7 +29599,7 @@
       </c>
       <c r="AG280" s="9"/>
     </row>
-    <row r="281" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B281" s="6" t="s">
         <v>1108</v>
       </c>
@@ -29687,7 +29687,7 @@
       </c>
       <c r="AG281" s="9"/>
     </row>
-    <row r="282" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B282" s="6" t="s">
         <v>1109</v>
       </c>
@@ -29770,7 +29770,7 @@
       </c>
       <c r="AG282" s="9"/>
     </row>
-    <row r="283" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B283" s="6" t="s">
         <v>1110</v>
       </c>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="AG283" s="9"/>
     </row>
-    <row r="284" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B284" s="6" t="s">
         <v>1113</v>
       </c>
@@ -29941,7 +29941,7 @@
       </c>
       <c r="AG284" s="9"/>
     </row>
-    <row r="285" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B285" s="6" t="s">
         <v>1114</v>
       </c>
@@ -30029,7 +30029,7 @@
       </c>
       <c r="AG285" s="9"/>
     </row>
-    <row r="286" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B286" s="6" t="s">
         <v>1115</v>
       </c>
@@ -30131,7 +30131,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="287" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B287" s="6" t="s">
         <v>1124</v>
       </c>
@@ -30211,7 +30211,7 @@
       </c>
       <c r="AG287" s="9"/>
     </row>
-    <row r="288" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B288" s="6" t="s">
         <v>1128</v>
       </c>
@@ -30296,7 +30296,7 @@
       </c>
       <c r="AG288" s="9"/>
     </row>
-    <row r="289" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B289" s="6" t="s">
         <v>1136</v>
       </c>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="AG289" s="9"/>
     </row>
-    <row r="290" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B290" s="6" t="s">
         <v>1141</v>
       </c>
@@ -30486,7 +30486,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="291" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B291" s="6" t="s">
         <v>1145</v>
       </c>
@@ -30596,7 +30596,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="292" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B292" s="6" t="s">
         <v>1156</v>
       </c>
@@ -30706,7 +30706,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="293" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B293" s="6" t="s">
         <v>1166</v>
       </c>
@@ -30816,7 +30816,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="294" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B294" s="6" t="s">
         <v>1172</v>
       </c>
@@ -30898,7 +30898,7 @@
       </c>
       <c r="AG294" s="9"/>
     </row>
-    <row r="295" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B295" s="6" t="s">
         <v>1177</v>
       </c>
@@ -30980,7 +30980,7 @@
       </c>
       <c r="AG295" s="9"/>
     </row>
-    <row r="296" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:37" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B296" s="6" t="s">
         <v>1178</v>
       </c>
@@ -31085,6 +31085,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c95907cf-e9f9-4b92-a10f-5d23f887974d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E03E5363D60F6E41BBDBD2986891499D" ma:contentTypeVersion="11" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="723753e909a658b81c41a8b79ae01792">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c95907cf-e9f9-4b92-a10f-5d23f887974d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e3777ca4d9a00e3a0fcbf4dc5e7e1334" ns2:_="">
     <xsd:import namespace="c95907cf-e9f9-4b92-a10f-5d23f887974d"/>
@@ -31268,16 +31278,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c95907cf-e9f9-4b92-a10f-5d23f887974d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -31288,24 +31288,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82F1485-9B46-4DE7-8EF4-68C318268E4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c95907cf-e9f9-4b92-a10f-5d23f887974d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55D8B328-D93F-4E0D-94E2-653BFEE7AE74}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -31324,6 +31306,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82F1485-9B46-4DE7-8EF4-68C318268E4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c95907cf-e9f9-4b92-a10f-5d23f887974d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DF01CBF-A5C4-4282-859D-8EAB800F0387}">
   <ds:schemaRefs>

--- a/plants_data/SFI_ALD_Petrochemicals_Sample_EU_NA_Apr_2022.xlsx
+++ b/plants_data/SFI_ALD_Petrochemicals_Sample_EU_NA_Apr_2022.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F43BD36-195D-4E5C-A9BB-7D22240CA980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D002E6C-A9AD-4E58-9E5C-A51DD8D9B1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11760" yWindow="12864" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{49FED9BB-E9B4-4298-B606-A2033C4439F2}"/>
+    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{49FED9BB-E9B4-4298-B606-A2033C4439F2}"/>
   </bookViews>
   <sheets>
     <sheet name="About - General" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5858" uniqueCount="1436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5858" uniqueCount="1437">
   <si>
     <t>Spatial Finance Initiative Petrochemicals Database for Europe and North America (April 2022)</t>
   </si>
@@ -4474,6 +4474,9 @@
   </si>
   <si>
     <t>NL3</t>
+  </si>
+  <si>
+    <t>NL4</t>
   </si>
 </sst>
 </file>
@@ -13551,7 +13554,7 @@
     </row>
     <row r="87" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>574</v>
@@ -13639,7 +13642,7 @@
     </row>
     <row r="88" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>579</v>
@@ -13727,7 +13730,7 @@
     </row>
     <row r="89" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>580</v>
@@ -13815,7 +13818,7 @@
     </row>
     <row r="90" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>581</v>
@@ -13903,7 +13906,7 @@
     </row>
     <row r="91" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>582</v>
